--- a/backend/data/financials_by_company/1831.SR.xlsx
+++ b/backend/data/financials_by_company/1831.SR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB5"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,219 +692,121 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1893.582845</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.07179199999999999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>217624818</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26376</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26376</v>
-      </c>
-      <c r="G2" t="n">
-        <v>127482444</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33010001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1976806926</v>
-      </c>
-      <c r="J2" t="n">
-        <v>217651194</v>
-      </c>
-      <c r="K2" t="n">
-        <v>184641193</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-48269392</v>
-      </c>
-      <c r="M2" t="n">
-        <v>48006216</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>127457961.582845</v>
-      </c>
-      <c r="P2" t="n">
-        <v>127482444</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2087002855</v>
-      </c>
-      <c r="R2" t="n">
-        <v>360463</v>
-      </c>
-      <c r="S2" t="n">
-        <v>154890225</v>
-      </c>
-      <c r="T2" t="n">
-        <v>450161975</v>
-      </c>
-      <c r="U2" t="n">
-        <v>450000000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="X2" t="n">
-        <v>127482444</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>127482444</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>127482444</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>656750</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>126825694</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>126825694</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>9809283</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>136634977</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>8135966</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-1410290</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-1098101</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2508391</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-48269392</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>263176</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>48006216</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>148427725</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>110195929</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5583583</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>8876830</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>676536</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8200294</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>39186001</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>18547348</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>20638653</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>360463</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>258623654</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1976806926</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2235430580</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2235430580</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>1098884</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>1098884</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-307302.590459</v>
+        <v>374445.080759</v>
       </c>
       <c r="C3" t="n">
-        <v>0.091936</v>
+        <v>0.117244</v>
       </c>
       <c r="D3" t="n">
-        <v>186173639</v>
+        <v>162680154</v>
       </c>
       <c r="E3" t="n">
-        <v>-1386491</v>
+        <v>3193736</v>
       </c>
       <c r="F3" t="n">
-        <v>-3342562</v>
+        <v>3193736</v>
       </c>
       <c r="G3" t="n">
-        <v>100225936</v>
+        <v>113462364</v>
       </c>
       <c r="H3" t="n">
-        <v>32422431</v>
+        <v>29609031</v>
       </c>
       <c r="I3" t="n">
-        <v>1645743207</v>
+        <v>1454375956</v>
       </c>
       <c r="J3" t="n">
-        <v>184787148</v>
+        <v>165873890</v>
       </c>
       <c r="K3" t="n">
-        <v>152364717</v>
+        <v>136264859</v>
       </c>
       <c r="L3" t="n">
-        <v>-43031501</v>
+        <v>-10464019</v>
       </c>
       <c r="M3" t="n">
-        <v>44181690</v>
+        <v>10551899</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>105217266.409541</v>
+        <v>110643073.080759</v>
       </c>
       <c r="P3" t="n">
-        <v>100225936</v>
+        <v>113462364</v>
       </c>
       <c r="Q3" t="n">
-        <v>1781668246</v>
+        <v>1570926390</v>
       </c>
       <c r="R3" t="n">
-        <v>99791</v>
+        <v>646414</v>
       </c>
       <c r="S3" t="n">
-        <v>112962253</v>
+        <v>108202556</v>
       </c>
       <c r="T3" t="n">
         <v>450000000</v>
@@ -913,158 +815,156 @@
         <v>450000000</v>
       </c>
       <c r="V3" t="n">
-        <v>0.22</v>
+        <v>0.252</v>
       </c>
       <c r="W3" t="n">
-        <v>0.22</v>
+        <v>0.252</v>
       </c>
       <c r="X3" t="n">
-        <v>100225936</v>
+        <v>113462364</v>
       </c>
       <c r="Y3" t="n">
-        <v>100225936</v>
+        <v>113462364</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>100225936</v>
+        <v>113462364</v>
       </c>
       <c r="AB3" t="n">
-        <v>1988850</v>
+        <v>2488443</v>
       </c>
       <c r="AC3" t="n">
-        <v>98237086</v>
+        <v>110973921</v>
       </c>
       <c r="AD3" t="n">
-        <v>98237086</v>
+        <v>110973921</v>
       </c>
       <c r="AE3" t="n">
-        <v>9945941</v>
+        <v>14739039</v>
       </c>
       <c r="AF3" t="n">
-        <v>108183027</v>
+        <v>125712960</v>
       </c>
       <c r="AG3" t="n">
-        <v>5689176</v>
+        <v>4437366</v>
       </c>
       <c r="AH3" t="n">
-        <v>-4183457</v>
+        <v>33017</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1150504</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3377890</v>
-      </c>
+        <v>-33017</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>-43031501</v>
+        <v>-10464019</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1150189</v>
+        <v>-87880</v>
       </c>
       <c r="AM3" t="n">
-        <v>44181690</v>
+        <v>10551899</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>108350274</v>
+        <v>112668283</v>
       </c>
       <c r="AP3" t="n">
-        <v>135925039</v>
+        <v>116550434</v>
       </c>
       <c r="AQ3" t="n">
-        <v>25183277</v>
+        <v>9199123</v>
       </c>
       <c r="AR3" t="n">
-        <v>8158871</v>
+        <v>6195700</v>
       </c>
       <c r="AS3" t="n">
-        <v>539004</v>
+        <v>591440</v>
       </c>
       <c r="AT3" t="n">
-        <v>7619867</v>
+        <v>5604260</v>
       </c>
       <c r="AU3" t="n">
-        <v>34610622</v>
+        <v>33746061</v>
       </c>
       <c r="AV3" t="n">
-        <v>20226900</v>
+        <v>10575520</v>
       </c>
       <c r="AW3" t="n">
-        <v>14383722</v>
+        <v>23170541</v>
       </c>
       <c r="AX3" t="n">
-        <v>99791</v>
+        <v>646414</v>
       </c>
       <c r="AY3" t="n">
-        <v>244275313</v>
+        <v>229218717</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1645743207</v>
+        <v>1454375956</v>
       </c>
       <c r="BA3" t="n">
-        <v>1890018520</v>
+        <v>1683594673</v>
       </c>
       <c r="BB3" t="n">
-        <v>1890018520</v>
+        <v>1683594673</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>374445.080759</v>
+        <v>-307302.590459</v>
       </c>
       <c r="C4" t="n">
-        <v>0.117244</v>
+        <v>0.091936</v>
       </c>
       <c r="D4" t="n">
-        <v>162680154</v>
+        <v>186173639</v>
       </c>
       <c r="E4" t="n">
-        <v>3193736</v>
+        <v>-1386491</v>
       </c>
       <c r="F4" t="n">
-        <v>3193736</v>
+        <v>-3342562</v>
       </c>
       <c r="G4" t="n">
-        <v>113462364</v>
+        <v>100225936</v>
       </c>
       <c r="H4" t="n">
-        <v>29609031</v>
+        <v>32422431</v>
       </c>
       <c r="I4" t="n">
-        <v>1454375956</v>
+        <v>1645743207</v>
       </c>
       <c r="J4" t="n">
-        <v>165873890</v>
+        <v>184787148</v>
       </c>
       <c r="K4" t="n">
-        <v>136264859</v>
+        <v>152364717</v>
       </c>
       <c r="L4" t="n">
-        <v>-10464019</v>
+        <v>-43031501</v>
       </c>
       <c r="M4" t="n">
-        <v>10551899</v>
+        <v>44181690</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>110643073.080759</v>
+        <v>105217266.409541</v>
       </c>
       <c r="P4" t="n">
-        <v>113462364</v>
+        <v>100225936</v>
       </c>
       <c r="Q4" t="n">
-        <v>1570926390</v>
+        <v>1781668246</v>
       </c>
       <c r="R4" t="n">
-        <v>646414</v>
+        <v>99791</v>
       </c>
       <c r="S4" t="n">
-        <v>108202556</v>
+        <v>112962253</v>
       </c>
       <c r="T4" t="n">
         <v>450000000</v>
@@ -1073,261 +973,421 @@
         <v>450000000</v>
       </c>
       <c r="V4" t="n">
-        <v>0.252</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
-        <v>0.252</v>
+        <v>0.22</v>
       </c>
       <c r="X4" t="n">
-        <v>113462364</v>
+        <v>100225936</v>
       </c>
       <c r="Y4" t="n">
-        <v>113462364</v>
+        <v>100225936</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>113462364</v>
+        <v>100225936</v>
       </c>
       <c r="AB4" t="n">
-        <v>2488443</v>
+        <v>1988850</v>
       </c>
       <c r="AC4" t="n">
-        <v>110973921</v>
+        <v>98237086</v>
       </c>
       <c r="AD4" t="n">
-        <v>110973921</v>
+        <v>98237086</v>
       </c>
       <c r="AE4" t="n">
-        <v>14739039</v>
+        <v>9945941</v>
       </c>
       <c r="AF4" t="n">
-        <v>125712960</v>
+        <v>108183027</v>
       </c>
       <c r="AG4" t="n">
-        <v>4437366</v>
+        <v>5689176</v>
       </c>
       <c r="AH4" t="n">
-        <v>33017</v>
+        <v>-4183457</v>
       </c>
       <c r="AI4" t="n">
-        <v>-33017</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>-1150504</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3377890</v>
+      </c>
       <c r="AK4" t="n">
-        <v>-10464019</v>
+        <v>-43031501</v>
       </c>
       <c r="AL4" t="n">
-        <v>-87880</v>
+        <v>-1150189</v>
       </c>
       <c r="AM4" t="n">
-        <v>10551899</v>
+        <v>44181690</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>112668283</v>
+        <v>108350274</v>
       </c>
       <c r="AP4" t="n">
-        <v>116550434</v>
+        <v>135925039</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9199123</v>
+        <v>25183277</v>
       </c>
       <c r="AR4" t="n">
-        <v>6195700</v>
+        <v>8158871</v>
       </c>
       <c r="AS4" t="n">
-        <v>591440</v>
+        <v>539004</v>
       </c>
       <c r="AT4" t="n">
-        <v>5604260</v>
+        <v>7619867</v>
       </c>
       <c r="AU4" t="n">
-        <v>33746061</v>
+        <v>34610622</v>
       </c>
       <c r="AV4" t="n">
-        <v>10575520</v>
+        <v>20226900</v>
       </c>
       <c r="AW4" t="n">
-        <v>23170541</v>
+        <v>14383722</v>
       </c>
       <c r="AX4" t="n">
-        <v>646414</v>
+        <v>99791</v>
       </c>
       <c r="AY4" t="n">
-        <v>229218717</v>
+        <v>244275313</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1454375956</v>
+        <v>1645743207</v>
       </c>
       <c r="BA4" t="n">
-        <v>1683594673</v>
+        <v>1890018520</v>
       </c>
       <c r="BB4" t="n">
-        <v>1683594673</v>
+        <v>1890018520</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1155557.318193</v>
+        <v>1402.877254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.096593</v>
+        <v>0.053188</v>
       </c>
       <c r="D5" t="n">
-        <v>171590537</v>
+        <v>265417700</v>
       </c>
       <c r="E5" t="n">
-        <v>11963203</v>
+        <v>26376</v>
       </c>
       <c r="F5" t="n">
-        <v>11963203</v>
+        <v>26376</v>
       </c>
       <c r="G5" t="n">
-        <v>144925035</v>
+        <v>175275326</v>
       </c>
       <c r="H5" t="n">
-        <v>23123386</v>
+        <v>33010001</v>
       </c>
       <c r="I5" t="n">
-        <v>1098830452</v>
+        <v>1976806926</v>
       </c>
       <c r="J5" t="n">
-        <v>183553740</v>
+        <v>265444076</v>
       </c>
       <c r="K5" t="n">
-        <v>160430354</v>
+        <v>232434075</v>
       </c>
       <c r="L5" t="n">
-        <v>-499240</v>
+        <v>-48269392</v>
       </c>
       <c r="M5" t="n">
-        <v>1211623</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1098884</v>
-      </c>
+        <v>48006216</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>134117389.318193</v>
+        <v>175250352.877254</v>
       </c>
       <c r="P5" t="n">
-        <v>144925035</v>
+        <v>175275326</v>
       </c>
       <c r="Q5" t="n">
-        <v>1172313115</v>
+        <v>2087002855</v>
       </c>
       <c r="R5" t="n">
-        <v>1585668</v>
+        <v>360463</v>
       </c>
       <c r="S5" t="n">
-        <v>146028932</v>
+        <v>154890225</v>
       </c>
       <c r="T5" t="n">
-        <v>450000000</v>
+        <v>450161975</v>
       </c>
       <c r="U5" t="n">
         <v>450000000</v>
       </c>
       <c r="V5" t="n">
-        <v>0.321667</v>
+        <v>0.39</v>
       </c>
       <c r="W5" t="n">
-        <v>0.321667</v>
+        <v>0.39</v>
       </c>
       <c r="X5" t="n">
-        <v>144925035</v>
+        <v>175275326</v>
       </c>
       <c r="Y5" t="n">
-        <v>144925035</v>
+        <v>175275326</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>144925035</v>
+        <v>175275326</v>
       </c>
       <c r="AB5" t="n">
-        <v>1085661</v>
+        <v>656750</v>
       </c>
       <c r="AC5" t="n">
-        <v>143839374</v>
+        <v>174618576</v>
       </c>
       <c r="AD5" t="n">
-        <v>143839374</v>
+        <v>174618576</v>
       </c>
       <c r="AE5" t="n">
-        <v>15379357</v>
+        <v>9809283</v>
       </c>
       <c r="AF5" t="n">
-        <v>159218731</v>
+        <v>184427859</v>
       </c>
       <c r="AG5" t="n">
-        <v>3280272</v>
+        <v>8135966</v>
       </c>
       <c r="AH5" t="n">
-        <v>10690411</v>
+        <v>-1410290</v>
       </c>
       <c r="AI5" t="n">
-        <v>-10690411</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>-1098101</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2508391</v>
+      </c>
       <c r="AK5" t="n">
-        <v>-499240</v>
+        <v>-48269392</v>
       </c>
       <c r="AL5" t="n">
-        <v>-712383</v>
+        <v>263176</v>
       </c>
       <c r="AM5" t="n">
-        <v>1211623</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1098884</v>
-      </c>
+        <v>48006216</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>146415433</v>
+        <v>148427725</v>
       </c>
       <c r="AP5" t="n">
-        <v>73482663</v>
+        <v>110195929</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-2056353</v>
+        <v>5583583</v>
       </c>
       <c r="AR5" t="n">
-        <v>6501364</v>
+        <v>8876830</v>
       </c>
       <c r="AS5" t="n">
-        <v>514170</v>
+        <v>676536</v>
       </c>
       <c r="AT5" t="n">
-        <v>5987194</v>
+        <v>8200294</v>
       </c>
       <c r="AU5" t="n">
-        <v>28282544</v>
+        <v>39186001</v>
       </c>
       <c r="AV5" t="n">
-        <v>10090736</v>
+        <v>18547348</v>
       </c>
       <c r="AW5" t="n">
-        <v>18191808</v>
+        <v>20638653</v>
       </c>
       <c r="AX5" t="n">
-        <v>1585668</v>
+        <v>360463</v>
       </c>
       <c r="AY5" t="n">
-        <v>219898096</v>
+        <v>258623654</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1098830452</v>
+        <v>1976806926</v>
       </c>
       <c r="BA5" t="n">
-        <v>1318728548</v>
+        <v>2235430580</v>
       </c>
       <c r="BB5" t="n">
-        <v>1318728548</v>
+        <v>2235430580</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4996539.095829</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.050706</v>
+      </c>
+      <c r="D6" t="n">
+        <v>265013491</v>
+      </c>
+      <c r="E6" t="n">
+        <v>98848739</v>
+      </c>
+      <c r="F6" t="n">
+        <v>98539636</v>
+      </c>
+      <c r="G6" t="n">
+        <v>272767065</v>
+      </c>
+      <c r="H6" t="n">
+        <v>31938296</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2784974829</v>
+      </c>
+      <c r="J6" t="n">
+        <v>363862230</v>
+      </c>
+      <c r="K6" t="n">
+        <v>331923934</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-44202932</v>
+      </c>
+      <c r="M6" t="n">
+        <v>44587207</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>179533071.095829</v>
+      </c>
+      <c r="P6" t="n">
+        <v>272767065</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2913262396</v>
+      </c>
+      <c r="R6" t="n">
+        <v>304639</v>
+      </c>
+      <c r="S6" t="n">
+        <v>200720349</v>
+      </c>
+      <c r="T6" t="n">
+        <v>451552547</v>
+      </c>
+      <c r="U6" t="n">
+        <v>450000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="X6" t="n">
+        <v>272767065</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>272767065</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>272767065</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>272767065</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>272767065</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>14569662</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>287336727</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>8572190</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>97257180</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-109635805</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>12069522</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-44202932</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-384275</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>44587207</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>199200263</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>128287567</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4394084</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>8102104</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>775639</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7326465</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>46133685</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>25839534</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>20294151</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>304639</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>327487830</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2784974829</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3112462659</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3112462659</v>
       </c>
     </row>
   </sheetData>
@@ -1341,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU5"/>
+  <dimension ref="A1:BW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1705,390 +1765,274 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>Other Equity Interest</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>450000000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>475000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>573250441</v>
-      </c>
-      <c r="F2" t="n">
-        <v>647395363</v>
-      </c>
-      <c r="G2" t="n">
-        <v>619700284</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1232086237</v>
-      </c>
-      <c r="I2" t="n">
-        <v>349728482</v>
-      </c>
-      <c r="J2" t="n">
-        <v>619700284</v>
-      </c>
-      <c r="K2" t="n">
-        <v>40427153</v>
-      </c>
-      <c r="L2" t="n">
-        <v>625118027</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1207075737</v>
-      </c>
-      <c r="N2" t="n">
-        <v>625118027</v>
-      </c>
-      <c r="O2" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>434347</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>99574659</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>625118027</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>93780281</v>
-      </c>
-      <c r="S2" t="n">
-        <v>475000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>475000000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1245167542</v>
-      </c>
-      <c r="V2" t="n">
-        <v>747586287</v>
-      </c>
-      <c r="W2" t="n">
-        <v>41222587</v>
-      </c>
-      <c r="X2" t="n">
-        <v>103238136</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>603125564</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>21167854</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>581957710</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>497581255</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>77317308</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11530868</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>44269799</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>19259299</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>25010500</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>131775900</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>64553935</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>5286176</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>18180417</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>41087342</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1870285569</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1022975832</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>25907882</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4747200</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4747200</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>750614145</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>36792042</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5417743</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2107104</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3310639</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>193359386</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-168214995</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>361574381</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>109570702</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>97957623</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>115102406</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>38943650</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>847309737</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>150064530</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>14260429</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>78654222</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>172268421</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>326876766</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-33279806</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>360156572</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>105185369</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>71467600</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>33717769</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>33717769</v>
-      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
-        <v>25000000</v>
-      </c>
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>450000000</v>
       </c>
       <c r="D3" t="n">
-        <v>475000000</v>
+        <v>450000000</v>
       </c>
       <c r="E3" t="n">
-        <v>483629203</v>
+        <v>479034035</v>
       </c>
       <c r="F3" t="n">
-        <v>612527013</v>
+        <v>593826823</v>
       </c>
       <c r="G3" t="n">
-        <v>562863548</v>
+        <v>547429524</v>
       </c>
       <c r="H3" t="n">
-        <v>1131556603</v>
+        <v>1117910230</v>
       </c>
       <c r="I3" t="n">
-        <v>212909936</v>
+        <v>234532675</v>
       </c>
       <c r="J3" t="n">
-        <v>562863548</v>
+        <v>547429524</v>
       </c>
       <c r="K3" t="n">
-        <v>49919303</v>
+        <v>31219113</v>
       </c>
       <c r="L3" t="n">
-        <v>568948893</v>
+        <v>555302520</v>
       </c>
       <c r="M3" t="n">
-        <v>1113426166</v>
+        <v>1117910230</v>
       </c>
       <c r="N3" t="n">
-        <v>566241917</v>
+        <v>554556659</v>
       </c>
       <c r="O3" t="n">
-        <v>-2706976</v>
+        <v>-745861</v>
       </c>
       <c r="P3" t="n">
-        <v>568948893</v>
+        <v>555302520</v>
       </c>
       <c r="Q3" t="n">
-        <v>25000000</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>36512439</v>
+        <v>103491296</v>
       </c>
       <c r="S3" t="n">
-        <v>475000000</v>
+        <v>375000000</v>
       </c>
       <c r="T3" t="n">
-        <v>475000000</v>
+        <v>375000000</v>
       </c>
       <c r="U3" t="n">
-        <v>1180736798</v>
+        <v>1150504852</v>
       </c>
       <c r="V3" t="n">
-        <v>692224696</v>
+        <v>695191736</v>
       </c>
       <c r="W3" t="n">
-        <v>22794346</v>
+        <v>17487811</v>
       </c>
       <c r="X3" t="n">
-        <v>95227910</v>
+        <v>83877102</v>
       </c>
       <c r="Y3" t="n">
-        <v>574202440</v>
+        <v>593826823</v>
       </c>
       <c r="Z3" t="n">
-        <v>29725167</v>
+        <v>31219113</v>
       </c>
       <c r="AA3" t="n">
-        <v>544477273</v>
+        <v>562607710</v>
       </c>
       <c r="AB3" t="n">
-        <v>488512102</v>
+        <v>455313116</v>
       </c>
       <c r="AC3" t="n">
-        <v>83928077</v>
+        <v>81653327</v>
       </c>
       <c r="AD3" t="n">
-        <v>14345688</v>
+        <v>15745030</v>
       </c>
       <c r="AE3" t="n">
-        <v>38324573</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>20194136</v>
+        <v>11026528</v>
       </c>
       <c r="AG3" t="n">
-        <v>18130437</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>101553448</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>96785567</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>753742</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>60858521</v>
+        <v>225882268</v>
       </c>
       <c r="AK3" t="n">
-        <v>5294000</v>
+        <v>2950999</v>
       </c>
       <c r="AL3" t="n">
-        <v>21981470</v>
+        <v>15630486</v>
       </c>
       <c r="AM3" t="n">
-        <v>33583051</v>
+        <v>225882268</v>
       </c>
       <c r="AN3" t="n">
-        <v>1746978715</v>
+        <v>1705061511</v>
       </c>
       <c r="AO3" t="n">
-        <v>1045556677</v>
+        <v>1015215720</v>
       </c>
       <c r="AP3" t="n">
-        <v>12858898</v>
+        <v>26070772</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11496186</v>
+        <v>13985656</v>
       </c>
       <c r="AR3" t="n">
-        <v>11496186</v>
+        <v>13985656</v>
       </c>
       <c r="AS3" t="n">
-        <v>70283710</v>
+        <v>25099306</v>
       </c>
       <c r="AT3" t="n">
-        <v>787425954</v>
+        <v>753064575</v>
       </c>
       <c r="AU3" t="n">
-        <v>785585868</v>
+        <v>753064575</v>
       </c>
       <c r="AV3" t="n">
-        <v>37295810</v>
+        <v>37799578</v>
       </c>
       <c r="AW3" t="n">
-        <v>6085345</v>
+        <v>7872996</v>
       </c>
       <c r="AX3" t="n">
-        <v>2774706</v>
+        <v>7872996</v>
       </c>
       <c r="AY3" t="n">
-        <v>3310639</v>
+        <v>5269787</v>
       </c>
       <c r="AZ3" t="n">
-        <v>173766832</v>
+        <v>165019678</v>
       </c>
       <c r="BA3" t="n">
-        <v>-149325735</v>
+        <v>-125569183</v>
       </c>
       <c r="BB3" t="n">
-        <v>323092567</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>165019678</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
       <c r="BD3" t="n">
-        <v>104455223</v>
+        <v>165019678</v>
       </c>
       <c r="BE3" t="n">
-        <v>89366815</v>
+        <v>80267767</v>
       </c>
       <c r="BF3" t="n">
-        <v>96172015</v>
+        <v>93009956</v>
       </c>
       <c r="BG3" t="n">
         <v>33098514</v>
@@ -2097,217 +2041,217 @@
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>701422038</v>
+        <v>689845791</v>
       </c>
       <c r="BJ3" t="n">
-        <v>124751381</v>
+        <v>244096988</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>721487</v>
       </c>
       <c r="BL3" t="n">
-        <v>68052919</v>
+        <v>57089396</v>
       </c>
       <c r="BM3" t="n">
-        <v>80075305</v>
+        <v>93098961</v>
       </c>
       <c r="BN3" t="n">
-        <v>269280216</v>
+        <v>243976861</v>
       </c>
       <c r="BO3" t="n">
-        <v>-48068887</v>
+        <v>-35649062</v>
       </c>
       <c r="BP3" t="n">
-        <v>317349103</v>
+        <v>279625923</v>
       </c>
       <c r="BQ3" t="n">
-        <v>159262217</v>
+        <v>108672981</v>
       </c>
       <c r="BR3" t="n">
-        <v>80283710</v>
+        <v>25099306</v>
       </c>
       <c r="BS3" t="n">
-        <v>78978507</v>
+        <v>83573675</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>20729369</v>
       </c>
       <c r="BU3" t="n">
-        <v>78978507</v>
-      </c>
+        <v>62844306</v>
+      </c>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>25000000</v>
+      </c>
       <c r="C4" t="n">
         <v>450000000</v>
       </c>
       <c r="D4" t="n">
-        <v>450000000</v>
+        <v>475000000</v>
       </c>
       <c r="E4" t="n">
-        <v>479034035</v>
+        <v>483629203</v>
       </c>
       <c r="F4" t="n">
-        <v>593826823</v>
+        <v>612527013</v>
       </c>
       <c r="G4" t="n">
-        <v>547429524</v>
+        <v>562863548</v>
       </c>
       <c r="H4" t="n">
-        <v>1117910230</v>
+        <v>1131556603</v>
       </c>
       <c r="I4" t="n">
-        <v>234532675</v>
+        <v>212909936</v>
       </c>
       <c r="J4" t="n">
-        <v>547429524</v>
+        <v>562863548</v>
       </c>
       <c r="K4" t="n">
-        <v>31219113</v>
+        <v>49919303</v>
       </c>
       <c r="L4" t="n">
-        <v>555302520</v>
+        <v>568948893</v>
       </c>
       <c r="M4" t="n">
-        <v>1117910230</v>
+        <v>1113426166</v>
       </c>
       <c r="N4" t="n">
-        <v>554556659</v>
+        <v>566241917</v>
       </c>
       <c r="O4" t="n">
-        <v>-745861</v>
+        <v>-2706976</v>
       </c>
       <c r="P4" t="n">
-        <v>555302520</v>
+        <v>568948893</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>25000000</v>
       </c>
       <c r="R4" t="n">
-        <v>103491296</v>
+        <v>36512439</v>
       </c>
       <c r="S4" t="n">
-        <v>375000000</v>
+        <v>475000000</v>
       </c>
       <c r="T4" t="n">
-        <v>375000000</v>
+        <v>475000000</v>
       </c>
       <c r="U4" t="n">
-        <v>1150504852</v>
+        <v>1180736798</v>
       </c>
       <c r="V4" t="n">
-        <v>695191736</v>
+        <v>692224696</v>
       </c>
       <c r="W4" t="n">
-        <v>17487811</v>
+        <v>22794346</v>
       </c>
       <c r="X4" t="n">
-        <v>83877102</v>
+        <v>95227910</v>
       </c>
       <c r="Y4" t="n">
-        <v>593826823</v>
+        <v>574202440</v>
       </c>
       <c r="Z4" t="n">
-        <v>31219113</v>
+        <v>29725167</v>
       </c>
       <c r="AA4" t="n">
-        <v>562607710</v>
+        <v>544477273</v>
       </c>
       <c r="AB4" t="n">
-        <v>455313116</v>
+        <v>488512102</v>
       </c>
       <c r="AC4" t="n">
-        <v>81653327</v>
+        <v>83928077</v>
       </c>
       <c r="AD4" t="n">
-        <v>15745030</v>
+        <v>14345688</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>38324573</v>
       </c>
       <c r="AF4" t="n">
-        <v>11026528</v>
+        <v>20194136</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>18130437</v>
       </c>
       <c r="AH4" t="n">
-        <v>96785567</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>753742</v>
-      </c>
+        <v>113199342</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>225882268</v>
+        <v>60858521</v>
       </c>
       <c r="AK4" t="n">
-        <v>2950999</v>
+        <v>5294000</v>
       </c>
       <c r="AL4" t="n">
-        <v>15630486</v>
+        <v>21981470</v>
       </c>
       <c r="AM4" t="n">
-        <v>225882268</v>
+        <v>33583051</v>
       </c>
       <c r="AN4" t="n">
-        <v>1705061511</v>
+        <v>1746978715</v>
       </c>
       <c r="AO4" t="n">
-        <v>1015215720</v>
+        <v>1045556677</v>
       </c>
       <c r="AP4" t="n">
-        <v>26070772</v>
+        <v>12858898</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13985656</v>
+        <v>11496186</v>
       </c>
       <c r="AR4" t="n">
-        <v>13985656</v>
+        <v>11496186</v>
       </c>
       <c r="AS4" t="n">
-        <v>25099306</v>
+        <v>70283710</v>
       </c>
       <c r="AT4" t="n">
-        <v>753064575</v>
+        <v>787425954</v>
       </c>
       <c r="AU4" t="n">
-        <v>753064575</v>
+        <v>785585868</v>
       </c>
       <c r="AV4" t="n">
-        <v>37799578</v>
+        <v>37295810</v>
       </c>
       <c r="AW4" t="n">
-        <v>7872996</v>
+        <v>6085345</v>
       </c>
       <c r="AX4" t="n">
-        <v>7872996</v>
+        <v>2774706</v>
       </c>
       <c r="AY4" t="n">
-        <v>5269787</v>
+        <v>3310639</v>
       </c>
       <c r="AZ4" t="n">
-        <v>165019678</v>
+        <v>173766832</v>
       </c>
       <c r="BA4" t="n">
-        <v>-125569183</v>
+        <v>-149325735</v>
       </c>
       <c r="BB4" t="n">
-        <v>165019678</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
+        <v>323092567</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>165019678</v>
+        <v>104455223</v>
       </c>
       <c r="BE4" t="n">
-        <v>80267767</v>
+        <v>89366815</v>
       </c>
       <c r="BF4" t="n">
-        <v>93009956</v>
+        <v>96172015</v>
       </c>
       <c r="BG4" t="n">
         <v>33098514</v>
@@ -2316,246 +2260,483 @@
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>689845791</v>
+        <v>701422038</v>
       </c>
       <c r="BJ4" t="n">
-        <v>244096988</v>
+        <v>124751381</v>
       </c>
       <c r="BK4" t="n">
-        <v>721487</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>57089396</v>
+        <v>68052919</v>
       </c>
       <c r="BM4" t="n">
-        <v>93098961</v>
+        <v>80075305</v>
       </c>
       <c r="BN4" t="n">
-        <v>243976861</v>
+        <v>269280216</v>
       </c>
       <c r="BO4" t="n">
-        <v>-35649062</v>
+        <v>-48068887</v>
       </c>
       <c r="BP4" t="n">
-        <v>279625923</v>
+        <v>317349103</v>
       </c>
       <c r="BQ4" t="n">
-        <v>108672981</v>
+        <v>159262217</v>
       </c>
       <c r="BR4" t="n">
-        <v>25099306</v>
+        <v>80283710</v>
       </c>
       <c r="BS4" t="n">
-        <v>83573675</v>
+        <v>78978507</v>
       </c>
       <c r="BT4" t="n">
-        <v>20729369</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>62844306</v>
-      </c>
+        <v>78978507</v>
+      </c>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>25000000</v>
+      </c>
       <c r="C5" t="n">
         <v>450000000</v>
       </c>
       <c r="D5" t="n">
-        <v>450000000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>475000000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>573250441</v>
+      </c>
       <c r="F5" t="n">
-        <v>24350964</v>
+        <v>647395363</v>
       </c>
       <c r="G5" t="n">
-        <v>564796161</v>
+        <v>667627484</v>
       </c>
       <c r="H5" t="n">
-        <v>572438747</v>
+        <v>1280013437</v>
       </c>
       <c r="I5" t="n">
-        <v>293140467</v>
+        <v>349728482</v>
       </c>
       <c r="J5" t="n">
-        <v>564796161</v>
+        <v>667627484</v>
       </c>
       <c r="K5" t="n">
-        <v>24350964</v>
+        <v>40427153</v>
       </c>
       <c r="L5" t="n">
-        <v>572438747</v>
+        <v>673045227</v>
       </c>
       <c r="M5" t="n">
-        <v>572438747</v>
+        <v>1255002937</v>
       </c>
       <c r="N5" t="n">
-        <v>570951856</v>
+        <v>673045227</v>
       </c>
       <c r="O5" t="n">
-        <v>-1486891</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>572438747</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>673045227</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>25000000</v>
+      </c>
       <c r="R5" t="n">
-        <v>126790673</v>
+        <v>141573163</v>
       </c>
       <c r="S5" t="n">
-        <v>375000000</v>
+        <v>475000000</v>
       </c>
       <c r="T5" t="n">
-        <v>375000000</v>
+        <v>475000000</v>
       </c>
       <c r="U5" t="n">
-        <v>465234464</v>
+        <v>1245167542</v>
       </c>
       <c r="V5" t="n">
-        <v>89113323</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>747586287</v>
+      </c>
+      <c r="W5" t="n">
+        <v>41222587</v>
+      </c>
       <c r="X5" t="n">
-        <v>75140482</v>
+        <v>103238136</v>
       </c>
       <c r="Y5" t="n">
-        <v>13972841</v>
+        <v>603125564</v>
       </c>
       <c r="Z5" t="n">
-        <v>13972841</v>
+        <v>21167854</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>581957710</v>
       </c>
       <c r="AB5" t="n">
-        <v>376121141</v>
+        <v>497581255</v>
       </c>
       <c r="AC5" t="n">
-        <v>99136239</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>77317308</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>11530868</v>
+      </c>
       <c r="AE5" t="n">
-        <v>10378123</v>
+        <v>44269799</v>
       </c>
       <c r="AF5" t="n">
-        <v>10378123</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>19259299</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>25010500</v>
+      </c>
       <c r="AH5" t="n">
-        <v>78894482</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>434347</v>
-      </c>
+        <v>144545467</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>63615615</v>
+        <v>64553935</v>
       </c>
       <c r="AK5" t="n">
-        <v>2929999</v>
+        <v>5286176</v>
       </c>
       <c r="AL5" t="n">
-        <v>28779809</v>
+        <v>18180417</v>
       </c>
       <c r="AM5" t="n">
-        <v>31905807</v>
+        <v>41087342</v>
       </c>
       <c r="AN5" t="n">
-        <v>1036186320</v>
+        <v>1918212769</v>
       </c>
       <c r="AO5" t="n">
-        <v>366924712</v>
+        <v>1070903032</v>
       </c>
       <c r="AP5" t="n">
-        <v>51375741</v>
+        <v>25907882</v>
       </c>
       <c r="AQ5" t="n">
-        <v>99574659</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>99574659</v>
-      </c>
+        <v>4747200</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4747200</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>14065841</v>
+        <v>798541345</v>
       </c>
       <c r="AU5" t="n">
-        <v>14065841</v>
+        <v>798541345</v>
       </c>
       <c r="AV5" t="n">
-        <v>37952874</v>
+        <v>36792042</v>
       </c>
       <c r="AW5" t="n">
-        <v>7642586</v>
+        <v>5417743</v>
       </c>
       <c r="AX5" t="n">
-        <v>3192349</v>
+        <v>2107104</v>
       </c>
       <c r="AY5" t="n">
-        <v>4450237</v>
+        <v>3310639</v>
       </c>
       <c r="AZ5" t="n">
-        <v>152151403</v>
+        <v>193359386</v>
       </c>
       <c r="BA5" t="n">
-        <v>-99405882</v>
+        <v>-168214995</v>
       </c>
       <c r="BB5" t="n">
-        <v>251557285</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
+        <v>361574381</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>57168236</v>
+        <v>109570702</v>
       </c>
       <c r="BE5" t="n">
-        <v>70260889</v>
+        <v>97957623</v>
       </c>
       <c r="BF5" t="n">
-        <v>91029646</v>
+        <v>115102406</v>
       </c>
       <c r="BG5" t="n">
-        <v>33098514</v>
+        <v>38943650</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>669261608</v>
+        <v>847309737</v>
       </c>
       <c r="BJ5" t="n">
-        <v>266367700</v>
+        <v>150064530</v>
       </c>
       <c r="BK5" t="n">
-        <v>6350391</v>
+        <v>14260429</v>
       </c>
       <c r="BL5" t="n">
-        <v>6118468</v>
+        <v>70929809</v>
       </c>
       <c r="BM5" t="n">
-        <v>69002663</v>
+        <v>179992834</v>
       </c>
       <c r="BN5" t="n">
-        <v>182003390</v>
-      </c>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+        <v>326876766</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-33279806</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>360156572</v>
+      </c>
       <c r="BQ5" t="n">
-        <v>139418996</v>
+        <v>105185369</v>
       </c>
       <c r="BR5" t="n">
-        <v>50000000</v>
+        <v>71467600</v>
       </c>
       <c r="BS5" t="n">
-        <v>89418996</v>
+        <v>33717769</v>
       </c>
       <c r="BT5" t="n">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>69418996</v>
+        <v>33717769</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-180</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>450000000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>475000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>218862058</v>
+      </c>
+      <c r="F6" t="n">
+        <v>328628319</v>
+      </c>
+      <c r="G6" t="n">
+        <v>870168726</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1184071649</v>
+      </c>
+      <c r="I6" t="n">
+        <v>641591369</v>
+      </c>
+      <c r="J6" t="n">
+        <v>870168726</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20597609</v>
+      </c>
+      <c r="L6" t="n">
+        <v>876040939</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1101291558</v>
+      </c>
+      <c r="N6" t="n">
+        <v>876040939</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>876040939</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>348565755</v>
+      </c>
+      <c r="S6" t="n">
+        <v>475000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>475000000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1077392851</v>
+      </c>
+      <c r="V6" t="n">
+        <v>414944113</v>
+      </c>
+      <c r="W6" t="n">
+        <v>45614193</v>
+      </c>
+      <c r="X6" t="n">
+        <v>134885794</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>234444126</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>9193507</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>225250619</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>662448738</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>72142483</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>17297056</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>94184193</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>11404102</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>82780091</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>207194597</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>75045855</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>6035178</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>20505553</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>48505124</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1953433790</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>649393683</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>22956669</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>406583091</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>406583091</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>36288274</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5872213</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2870677</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3001536</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>171007515</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-159323576</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>330331091</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>77205396</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>99341435</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>116719410</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>37064850</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1304040107</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>193321104</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>12534301</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>62068313</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>292398611</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>493799070</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-41071153</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>534870223</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>249918708</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>160750056</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>89168652</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>20536248</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>68632404</v>
+      </c>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="n">
+        <v>654794</v>
       </c>
     </row>
   </sheetData>
@@ -2569,7 +2750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2823,583 +3004,682 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Sale Of Business</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Gain Loss On Sale Of Business</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>32183230</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-102765534</v>
-      </c>
-      <c r="D2" t="n">
-        <v>147126034</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-38926078</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33717769</v>
-      </c>
-      <c r="G2" t="n">
-        <v>78978507</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-45260738</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-90374721</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-1595182</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-46957525</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-65250000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>44360500</v>
-      </c>
-      <c r="N2" t="n">
-        <v>122938534</v>
-      </c>
-      <c r="O2" t="n">
-        <v>122938534</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-78578034</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-102765534</v>
-      </c>
-      <c r="R2" t="n">
-        <v>24187500</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-25995325</v>
-      </c>
-      <c r="T2" t="n">
-        <v>35182915</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-23930928</v>
-      </c>
-      <c r="V2" t="n">
-        <v>51169072</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-75100000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>-8934</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-8934</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-37238378</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1678766</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-38917144</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>71109308</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-12624103</v>
-      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>-115208050</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>7739160</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>50522347</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>10303687</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-71628606</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-112144638</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>45472086</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1210349</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4274490</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>33010001</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>676536</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>32333465</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>27800177</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-1436666</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-1098101</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>136634977</v>
-      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>133231712</v>
-      </c>
-      <c r="C3" t="n">
+        <v>180166307</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>562607710</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-13739160</v>
+      </c>
+      <c r="F3" t="n">
+        <v>83573675</v>
+      </c>
+      <c r="G3" t="n">
+        <v>89418996</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-5845321</v>
+      </c>
+      <c r="I3" t="n">
+        <v>422952428</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3381141</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-5925739</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-121875000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>562607710</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>562607710</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>562607710</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-622703216</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>128345911</v>
+      </c>
+      <c r="V3" t="n">
+        <v>128345911</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
+      <c r="X3" t="n">
+        <v>-346317</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-346317</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-737468509</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-737468509</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-2300</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-2300</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-13232001</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>504859</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-13736860</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>193905467</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-15600111</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>-15550337</v>
-      </c>
-      <c r="F3" t="n">
-        <v>78978507</v>
-      </c>
-      <c r="G3" t="n">
-        <v>83573675</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-4595168</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-139159823</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>-38101618</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-82500000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-14217394</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7755555</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-7993727</v>
-      </c>
-      <c r="V3" t="n">
-        <v>65006273</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-73000000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-710501</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-710501</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-13268721</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1571115</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-14839836</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>148782049</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-11345283</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>7755555</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>-15780523</v>
+        <v>51258124</v>
       </c>
       <c r="AK3" t="n">
-        <v>-3606947</v>
+        <v>5780017</v>
       </c>
       <c r="AL3" t="n">
-        <v>-84710280</v>
+        <v>72715595</v>
       </c>
       <c r="AM3" t="n">
-        <v>45277612</v>
+        <v>43992514</v>
       </c>
       <c r="AN3" t="n">
-        <v>69109156</v>
+        <v>28019831</v>
       </c>
       <c r="AO3" t="n">
-        <v>-41850064</v>
+        <v>-99249833</v>
       </c>
       <c r="AP3" t="n">
-        <v>67270390</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
+        <v>10485527</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>27723070</v>
+        <v>8372220</v>
       </c>
       <c r="AS3" t="n">
-        <v>32422431</v>
+        <v>29609031</v>
       </c>
       <c r="AT3" t="n">
-        <v>539004</v>
+        <v>591440</v>
       </c>
       <c r="AU3" t="n">
-        <v>32422431</v>
+        <v>29017591</v>
       </c>
       <c r="AV3" t="n">
-        <v>24806863</v>
+        <v>21340720</v>
       </c>
       <c r="AW3" t="n">
-        <v>-840895</v>
+        <v>-3160719</v>
       </c>
       <c r="AX3" t="n">
-        <v>-1150504</v>
+        <v>-33017</v>
       </c>
       <c r="AY3" t="n">
-        <v>105005017</v>
-      </c>
+        <v>125712960</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>180166307</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>133231712</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
       <c r="D4" t="n">
-        <v>562607710</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-13739160</v>
+        <v>-15550337</v>
       </c>
       <c r="F4" t="n">
+        <v>78978507</v>
+      </c>
+      <c r="G4" t="n">
         <v>83573675</v>
       </c>
-      <c r="G4" t="n">
-        <v>89418996</v>
-      </c>
       <c r="H4" t="n">
-        <v>-5845321</v>
+        <v>-4595168</v>
       </c>
       <c r="I4" t="n">
-        <v>422952428</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3381141</v>
-      </c>
+        <v>-139159823</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>-5925739</v>
+        <v>-38101618</v>
       </c>
       <c r="L4" t="n">
-        <v>-121875000</v>
+        <v>-82500000</v>
       </c>
       <c r="M4" t="n">
-        <v>562607710</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>562607710</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
       <c r="R4" t="n">
-        <v>562607710</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-622703216</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
+        <v>-14217394</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7755555</v>
+      </c>
       <c r="U4" t="n">
-        <v>128345911</v>
+        <v>-7993727</v>
       </c>
       <c r="V4" t="n">
-        <v>128345911</v>
+        <v>65006273</v>
       </c>
       <c r="W4" t="n">
+        <v>-73000000</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
-      <c r="X4" t="n">
-        <v>-346317</v>
-      </c>
       <c r="Y4" t="n">
-        <v>-346317</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-737468509</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-737468509</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2300</v>
+        <v>-710501</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2300</v>
+        <v>-710501</v>
       </c>
       <c r="AD4" t="n">
-        <v>-13232001</v>
+        <v>-13268721</v>
       </c>
       <c r="AE4" t="n">
-        <v>504859</v>
+        <v>1571115</v>
       </c>
       <c r="AF4" t="n">
-        <v>-13736860</v>
+        <v>-14839836</v>
       </c>
       <c r="AG4" t="n">
-        <v>193905467</v>
+        <v>148782049</v>
       </c>
       <c r="AH4" t="n">
-        <v>-15600111</v>
+        <v>-11345283</v>
       </c>
       <c r="AI4" t="n">
+        <v>7755555</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-15780523</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-3606947</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-84710280</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>45277612</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>69109156</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-41850064</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>67270390</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>51258124</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>5780017</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>72715595</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>43992514</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>28019831</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-99249833</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>10485527</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>8372220</v>
+        <v>27723070</v>
       </c>
       <c r="AS4" t="n">
-        <v>29609031</v>
+        <v>32422431</v>
       </c>
       <c r="AT4" t="n">
-        <v>591440</v>
+        <v>539004</v>
       </c>
       <c r="AU4" t="n">
-        <v>29017591</v>
+        <v>32422431</v>
       </c>
       <c r="AV4" t="n">
-        <v>21340720</v>
+        <v>24806863</v>
       </c>
       <c r="AW4" t="n">
-        <v>-3160719</v>
+        <v>-840895</v>
       </c>
       <c r="AX4" t="n">
-        <v>-33017</v>
+        <v>-1150504</v>
       </c>
       <c r="AY4" t="n">
-        <v>125712960</v>
-      </c>
+        <v>105005017</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>15485131</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>32183230</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-102765534</v>
+      </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>147126034</v>
       </c>
       <c r="E5" t="n">
-        <v>-12440536</v>
+        <v>-38926078</v>
       </c>
       <c r="F5" t="n">
-        <v>89418996</v>
+        <v>33717769</v>
       </c>
       <c r="G5" t="n">
-        <v>57909641</v>
+        <v>78978507</v>
       </c>
       <c r="H5" t="n">
-        <v>31509355</v>
+        <v>-45260738</v>
       </c>
       <c r="I5" t="n">
-        <v>-154576535</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>-90374721</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1595182</v>
+      </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-46957525</v>
       </c>
       <c r="L5" t="n">
-        <v>-140625000</v>
+        <v>-65250000</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>44360500</v>
+      </c>
+      <c r="N5" t="n">
+        <v>122938534</v>
+      </c>
+      <c r="O5" t="n">
+        <v>122938534</v>
+      </c>
       <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>-78578034</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-102765534</v>
+      </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>24187500</v>
       </c>
       <c r="S5" t="n">
-        <v>158160223</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>-25995325</v>
+      </c>
+      <c r="T5" t="n">
+        <v>35182915</v>
+      </c>
       <c r="U5" t="n">
-        <v>146225774</v>
+        <v>-23930928</v>
       </c>
       <c r="V5" t="n">
-        <v>244797471</v>
+        <v>51169072</v>
       </c>
       <c r="W5" t="n">
-        <v>-98571697</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
+        <v>-75100000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-769786</v>
+        <v>-8934</v>
       </c>
       <c r="AC5" t="n">
-        <v>-769786</v>
+        <v>-8934</v>
       </c>
       <c r="AD5" t="n">
-        <v>12704235</v>
+        <v>-37238378</v>
       </c>
       <c r="AE5" t="n">
-        <v>24374985</v>
+        <v>1678766</v>
       </c>
       <c r="AF5" t="n">
-        <v>-11670750</v>
+        <v>-38917144</v>
       </c>
       <c r="AG5" t="n">
-        <v>27925667</v>
+        <v>71109308</v>
       </c>
       <c r="AH5" t="n">
-        <v>-15249978</v>
+        <v>-12624103</v>
       </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-129029294</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>-115208050</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>7739160</v>
+      </c>
       <c r="AL5" t="n">
-        <v>2692593</v>
+        <v>50522347</v>
       </c>
       <c r="AM5" t="n">
-        <v>-48755211</v>
+        <v>10303687</v>
       </c>
       <c r="AN5" t="n">
-        <v>-104428397</v>
+        <v>-71628606</v>
       </c>
       <c r="AO5" t="n">
-        <v>21461721</v>
+        <v>-112144638</v>
       </c>
       <c r="AP5" t="n">
-        <v>-4852469</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
+        <v>45472086</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1210349</v>
+      </c>
       <c r="AR5" t="n">
-        <v>-4592477</v>
+        <v>4274490</v>
       </c>
       <c r="AS5" t="n">
-        <v>23123386</v>
+        <v>33010001</v>
       </c>
       <c r="AT5" t="n">
-        <v>514170</v>
+        <v>676536</v>
       </c>
       <c r="AU5" t="n">
-        <v>22609216</v>
+        <v>32333465</v>
       </c>
       <c r="AV5" t="n">
-        <v>20946199</v>
+        <v>27800177</v>
       </c>
       <c r="AW5" t="n">
-        <v>-1272792</v>
+        <v>-1436666</v>
       </c>
       <c r="AX5" t="n">
-        <v>-10690411</v>
+        <v>-1098101</v>
       </c>
       <c r="AY5" t="n">
-        <v>159218731</v>
+        <v>184427859</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-30734894</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-446648500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>147711000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-11041248</v>
+      </c>
+      <c r="F6" t="n">
+        <v>89168652</v>
+      </c>
+      <c r="G6" t="n">
+        <v>33717769</v>
+      </c>
+      <c r="H6" t="n">
+        <v>55450883</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-431122183</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>-41980518</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-67500000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-298937500</v>
+      </c>
+      <c r="N6" t="n">
+        <v>147711000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>147711000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-446648500</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-446648500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>506266712</v>
+      </c>
+      <c r="T6" t="n">
+        <v>37633300</v>
+      </c>
+      <c r="U6" t="n">
+        <v>36118192</v>
+      </c>
+      <c r="V6" t="n">
+        <v>96417692</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-60299500</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>434311080</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>-1539212</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-1539212</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-256648</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9245388</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-9502036</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-19693646</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-9458268</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>-283333090</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-461612</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-86731995</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>72882093</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-34854804</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-234166772</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>42992326</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9761341</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3013596</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>31938296</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>775639</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>31162657</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>45365655</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-1282456</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-4633143</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>287336727</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>434311080</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-105002662</v>
       </c>
     </row>
   </sheetData>
@@ -3413,7 +3693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EZ2"/>
+  <dimension ref="A1:FB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3849,350 +4129,360 @@
       </c>
       <c r="CI1" t="inlineStr">
         <is>
+          <t>recommendationMean</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>numberOfAnalystOpinions</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4214,10 +4504,8 @@
           <t>Riyadh</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>13124</t>
-        </is>
+      <c r="D2" t="n">
+        <v>13124</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4294,79 +4582,79 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>6.7</v>
+        <v>6.61</v>
       </c>
       <c r="V2" t="n">
-        <v>6.7</v>
+        <v>6.59</v>
       </c>
       <c r="W2" t="n">
-        <v>6.56</v>
+        <v>6.55</v>
       </c>
       <c r="X2" t="n">
-        <v>6.7</v>
+        <v>6.61</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.7</v>
+        <v>6.61</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.7</v>
+        <v>6.59</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.56</v>
+        <v>6.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.7</v>
+        <v>6.61</v>
       </c>
       <c r="AC2" t="n">
         <v>0.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="AE2" t="n">
         <v>1777248000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5</v>
+        <v>0.2308</v>
       </c>
       <c r="AG2" t="n">
         <v>3.63</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.224</v>
+        <v>0.257</v>
       </c>
       <c r="AI2" t="n">
-        <v>21.933332</v>
+        <v>10.123077</v>
       </c>
       <c r="AJ2" t="n">
         <v>14.304347</v>
       </c>
       <c r="AK2" t="n">
-        <v>2396722</v>
+        <v>1693595</v>
       </c>
       <c r="AL2" t="n">
-        <v>2396722</v>
+        <v>1693595</v>
       </c>
       <c r="AM2" t="n">
-        <v>4089070</v>
+        <v>3889741</v>
       </c>
       <c r="AN2" t="n">
-        <v>2335450</v>
+        <v>1864611</v>
       </c>
       <c r="AO2" t="n">
-        <v>2335450</v>
+        <v>1864611</v>
       </c>
       <c r="AP2" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>6.57</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6.6</v>
       </c>
       <c r="AR2" t="n">
         <v>2967890944</v>
       </c>
       <c r="AS2" t="n">
-        <v>3022016568</v>
+        <v>2967890898</v>
       </c>
       <c r="AT2" t="n">
         <v>4.39</v>
@@ -4384,16 +4672,16 @@
         <v>0.89269316</v>
       </c>
       <c r="AY2" t="n">
-        <v>6.1762</v>
+        <v>6.333</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.7663</v>
+        <v>5.8712</v>
       </c>
       <c r="BA2" t="n">
         <v>0.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.029850747</v>
+        <v>0.030257186</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -4416,19 +4704,19 @@
         <v>451047249</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.16726999</v>
+        <v>0.11684</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.01675</v>
+        <v>0.016210001</v>
       </c>
       <c r="BK2" t="n">
         <v>451047249</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.947</v>
+        <v>2.083</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.3795583</v>
+        <v>3.1589055</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4446,18 +4734,18 @@
         <v>293084224</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="BT2" t="n">
         <v>0.46</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>10:1</t>
+          <t>1.2632:1</t>
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>1707004800</v>
+        <v>1782777600</v>
       </c>
       <c r="BW2" t="n">
         <v>0.9</v>
@@ -4466,10 +4754,10 @@
         <v>11.959</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.30815113</v>
+        <v>0.44933915</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.27449715</v>
+        <v>0.2568333</v>
       </c>
       <c r="CA2" t="n">
         <v>0.13</v>
@@ -4492,259 +4780,267 @@
         <v>5.65</v>
       </c>
       <c r="CG2" t="n">
-        <v>6.8225</v>
+        <v>7.11</v>
       </c>
       <c r="CH2" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CJ2" t="n">
+        <v>7.295</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="CK2" t="n">
         <v>4</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>294002208</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>0.652</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>250317616</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>319555648</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>1.467</v>
       </c>
-      <c r="CP2" t="n">
+      <c r="CQ2" t="n">
         <v>1.903</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CR2" t="n">
         <v>3324648448</v>
       </c>
-      <c r="CR2" t="n">
+      <c r="CS2" t="n">
         <v>34.01</v>
       </c>
-      <c r="CS2" t="n">
+      <c r="CT2" t="n">
         <v>7.384</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CU2" t="n">
         <v>0.07435</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CV2" t="n">
         <v>0.37730998</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CW2" t="n">
         <v>366407616</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="CX2" t="n">
         <v>-59275872</v>
       </c>
-      <c r="CX2" t="n">
+      <c r="CY2" t="n">
         <v>-16842906</v>
       </c>
-      <c r="CY2" t="n">
+      <c r="CZ2" t="n">
         <v>0.417</v>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DA2" t="n">
         <v>0.299</v>
       </c>
-      <c r="DA2" t="n">
+      <c r="DB2" t="n">
         <v>0.11021</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="DC2" t="n">
         <v>0.075289994</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DD2" t="n">
         <v>0.0828</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>1831.SR</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DJ2" t="b">
+      <c r="DK2" t="b">
         <v>0</v>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DM2" t="n">
+        <v>-0.45386097</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="DO2" t="inlineStr">
         <is>
           <t>SAU</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>finmb_596168194</t>
         </is>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>Asia/Riyadh</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="DP2" t="n">
+      <c r="DS2" t="n">
         <v>10800000</v>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>sr_market</t>
         </is>
       </c>
-      <c r="DR2" t="b">
+      <c r="DU2" t="b">
         <v>0</v>
       </c>
-      <c r="DS2" t="n">
-        <v>-1.7910432</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="DV2" t="n">
-        <v>1780402785</v>
+        <v>1755518400</v>
       </c>
       <c r="DW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>12.901961</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.24699974</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.039002012</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.70879984</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0.120724864</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>1.8 - Buy</t>
+        </is>
+      </c>
+      <c r="EI2" t="b">
         <v>0</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>[{'header': 'Stock Dividend', 'message': '1831.SR announced a 26.32% stock dividend with an ex-date of Jun. 30, 2026', 'meta': {'eventType': 'STOCK_DIVIDEND', 'dateEpochMs': 1782766800000, 'percent': '26.32%'}}]</t>
+        </is>
+      </c>
+      <c r="EK2" t="n">
+        <v>1781785172</v>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>Maharah Human Resources Co.</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>Maharah for Human Resources Company</t>
+        </is>
+      </c>
+      <c r="EO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EP2" t="n">
         <v>1560927600000</v>
       </c>
-      <c r="DY2" t="n">
-        <v>-0.119999886</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>6.56 - 6.7</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EQ2" t="n">
+        <v>-0.03000021</v>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>6.55 - 6.61</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
         <is>
           <t>Saudi</t>
         </is>
       </c>
-      <c r="EB2" t="n">
-        <v>4089070</v>
-      </c>
-      <c r="EC2" t="n">
+      <c r="ET2" t="n">
+        <v>3889741</v>
+      </c>
+      <c r="EU2" t="n">
         <v>2.19</v>
       </c>
-      <c r="ED2" t="n">
+      <c r="EV2" t="n">
         <v>0.49886107</v>
       </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>Maharah for Human Resources Company</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>Maharah Human Resources Co.</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>13.16</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.4038</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.06538001</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0.8136997</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0.14111297</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ES2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET2" t="inlineStr">
+      <c r="EW2" t="inlineStr">
         <is>
           <t>4.39 - 6.91</t>
         </is>
       </c>
-      <c r="EU2" t="n">
+      <c r="EX2" t="n">
         <v>-0.32999992</v>
       </c>
-      <c r="EV2" t="n">
+      <c r="EY2" t="n">
         <v>-0.047756866</v>
       </c>
-      <c r="EW2" t="n">
-        <v>30.815113</v>
-      </c>
-      <c r="EX2" t="n">
+      <c r="EZ2" t="n">
+        <v>44.933914</v>
+      </c>
+      <c r="FA2" t="n">
         <v>1754996340</v>
       </c>
-      <c r="EY2" t="n">
-        <v>1755518400</v>
-      </c>
-      <c r="EZ2" t="inlineStr"/>
+      <c r="FB2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
